--- a/daily_matches/job_matches_2026-04-09.xlsx
+++ b/daily_matches/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI First Senior Software Engineer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Glue, Redshift, Kinesis, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dfa31e07ed5ab9</t>
+          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Gen AI, Java Full stack</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ConnectOne Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Data Lake, Apache Airflow, CI/CD, Git, Redshift, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, PyTorch, Keras, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c88aa2ee3a1d2797</t>
+          <t>https://www.indeed.com/viewjob?jk=e5d081aba84c9a03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Productivity</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Airwallex</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68bfb287bd62afc4</t>
+          <t>https://www.indeed.com/viewjob?jk=de236675c492e363</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist, Assessment &amp; Learning Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amira Learning</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, Git, Python, R, Bayesian, A/B Testing</t>
+          <t>RAG, Docker, CI/CD, Git, Kafka, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0806783dba50cb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c66086e2167d4be</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist, Assessment &amp; Learning Analytics</t>
+          <t>Senior AI/ML Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amira Learning</t>
+          <t>Vanguard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, Git, Python, R, Bayesian, A/B Testing</t>
+          <t>Generative AI, RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a4f87faad227bb</t>
+          <t>https://www.indeed.com/viewjob?jk=dcf7394d1f8d36ba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer/Developer - Midlevel (Hybrid- Philadelphia, PA)</t>
+          <t>Sr Associate - Devops Engineer - CIB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,29 +661,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, Docker, Kubernetes, Python, R</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a4ee9897215e889</t>
+          <t>https://www.indeed.com/viewjob?jk=48bf21b51aaefead</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Data Product APIs</t>
+          <t>Senior Production Engineer (Cloud Platform &amp; Reliability – Machine Identity Security) - hybrid</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>USA TODAY Co.</t>
+          <t>CyberArk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,46 +692,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df87b3ec4e35311</t>
+          <t>https://www.indeed.com/viewjob?jk=fd5f4cf613ca2254</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Data Product APIs</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USA TODAY Co.</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, PyTorch, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef65449e25c7a8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c113732ec4252e91</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Data Product APIs</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USA TODAY Co.</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e7431bbd4f12244</t>
+          <t>https://www.indeed.com/viewjob?jk=113526f40b0887f3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026 Analytics &amp; Data Science Intern</t>
+          <t>AI/ML Software Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,122 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, BigQuery, Redshift, Tableau, Python, SQL, R</t>
+          <t>Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8dc8dde271957d81</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer I (NUVO)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Inland Imaging</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Spokane Valley, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e47a61d2330d23df</t>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13218d00ab135fcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Peoria, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d5c6c7cf22e972d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sr Data Analyst</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lincare</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Clearwater, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-09.xlsx
+++ b/daily_matches/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Glue, Redshift, Kinesis, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Keras, BigQuery, Dataflow, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,77 +496,77 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daceb310871c5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Gen AI, Java Full stack</t>
+          <t>Software Engineer, Factory Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, PyTorch, Keras, CI/CD, Git, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5d081aba84c9a03</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a02ff37af5fef2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer, Factory Software</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de236675c492e363</t>
+          <t>https://www.indeed.com/viewjob?jk=bb24b9de242af793</t>
         </is>
       </c>
     </row>
@@ -578,12 +578,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, Kafka, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c66086e2167d4be</t>
+          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/ML Cloud Engineer</t>
+          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vanguard</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, MLflow, Snowflake, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcf7394d1f8d36ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Associate - Devops Engineer - CIB</t>
+          <t>Senior Full-Stack Engineer (AI-Augmented)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Omnizant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Port Washington, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Copilot, S3, EC2, CI/CD, Terraform, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48bf21b51aaefead</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6e1479b81a63df</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Production Engineer (Cloud Platform &amp; Reliability – Machine Identity Security) - hybrid</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CyberArk</t>
+          <t>The Mosaic Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd5f4cf613ca2254</t>
+          <t>https://www.indeed.com/viewjob?jk=ee0d9ff8fea4370a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineer - Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Joby Aviation</t>
+          <t>PDSSOFT INC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, PyTorch, CI/CD, Python, R, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c113732ec4252e91</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9a51386b1652cc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>AI Platform Architect (Teradyne, North Reading)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>North Reading, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, R</t>
+          <t>RAG, Copilot, Cortex, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113526f40b0887f3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4557ffcdb335fa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Senneca Holdings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Springdale, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,122 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Python, SQL, R</t>
+          <t>RAG, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dc8dde271957d81</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AI Solutions Engineer I (NUVO)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Inland Imaging</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Spokane Valley, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, Gemini, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13218d00ab135fcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Peoria, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5c6c7cf22e972d</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sr Data Analyst</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Lincare</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Clearwater, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bafbad52ee9c6a54</t>
+          <t>https://www.indeed.com/viewjob?jk=d3eccf033aeae942</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-09.xlsx
+++ b/daily_matches/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>N2IA Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Keras, BigQuery, Dataflow, BigQuery</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,94 +496,94 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5b55d7ce3a3210</t>
+          <t>https://www.indeed.com/viewjob?jk=a5765fbf481e4537</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer, Factory Software</t>
+          <t>Senior Software Engineer, Web Development</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Communify</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a02ff37af5fef2</t>
+          <t>https://www.indeed.com/viewjob?jk=f3befea356e71854</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer, Factory Software</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb24b9de242af793</t>
+          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>DDN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7db0adb04360b67</t>
+          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Distinguished Data Engineer - Enterprise Data Technology</t>
+          <t>Sr. Data Scientist - People Analytics - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Snowflake, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bb308be554a0dee</t>
+          <t>https://www.indeed.com/viewjob?jk=965e1624c3af1c79</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (AI-Augmented)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Omnizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Port Washington, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, CI/CD, Terraform, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6e1479b81a63df</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Mosaic Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0d9ff8fea4370a</t>
+          <t>https://www.indeed.com/viewjob?jk=3057572e5da91cd3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer - Senior</t>
+          <t>Data Scientist - Atlanta, GA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PDSSOFT INC</t>
+          <t>Cortland</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, RAG, S3, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9a51386b1652cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6e3a652eae42dd47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Platform Architect (Teradyne, North Reading)</t>
+          <t>Intern- Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>VBrick</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, GitHub Actions, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e4557ffcdb335fa</t>
+          <t>https://www.indeed.com/viewjob?jk=996d77616d403a3e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer - Systems</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Senneca Holdings</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Springdale, OH, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,52 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, RAG, TensorFlow, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81d0997d0f1407af</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3eccf033aeae942</t>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d91f510ddbac5fdf</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-09.xlsx
+++ b/daily_matches/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer with AI (FTE)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N2IA Technologies</t>
+          <t>Amplified Sourcing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, TensorFlow, BigQuery, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5765fbf481e4537</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef6a677ec45706f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Web Development</t>
+          <t>Sr. Engineer, Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Communify</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Prompt Engineering, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3befea356e71854</t>
+          <t>https://www.indeed.com/viewjob?jk=b6dcaf8ffd85fd5d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b3ec3709af933a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ed72dec4a4153ed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Gen AI Engineer (Remote)-6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DDN</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frederick, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Kafka, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35a412c42944021</t>
+          <t>https://www.indeed.com/viewjob?jk=742dbe1f38c1a6a9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist - People Analytics - Remote</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=965e1624c3af1c79</t>
+          <t>https://www.indeed.com/viewjob?jk=ce4901601fc9ef85</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Applications Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aries Aero Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, FAISS, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a67f69c448e7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=01d442ada28b09fb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Consultant, Data Scientist | Forensic and Litigation Consulting</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FTI Consulting, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, spaCy, MLflow, FastAPI, Docker, Git, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3057572e5da91cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b83670379818134</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist - Atlanta, GA</t>
+          <t>Python AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cortland</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, Pinecone, Prompt Engineering, S3, EC2, Glue, FastAPI, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e3a652eae42dd47</t>
+          <t>https://www.indeed.com/viewjob?jk=32db098f47b462ca</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Intern- Software Engineer</t>
+          <t>Software AI Engineer – Agentic AI-6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VBrick</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=996d77616d403a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b51936d889dfdd9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Systems</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>GameChanger</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, BigQuery, Data Lake, GitHub Actions, Git, Snowflake, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,462 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0997d0f1407af</t>
+          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Axios</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=208813262e2d55e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer — Builder Wanted - AI Tech Startup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FutureStack AI Inc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, FastAPI, Docker, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0503c5c69f5d27c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer – Equities Technology</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>William Blair &amp; Company</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Synapse, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28f10cecc44333b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Treeswift</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb8792d87cb5d68a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Mid-Level Engineer, Global</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85b38a3aeca26ed5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Apache Airflow, CI/CD, Terraform, Git, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b09c8dba3c2b63ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Machine Learning Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>k1x</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, MLflow, Docker, Kubernetes, CI/CD, Git, Snowflake, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c670dfb6481a8e15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>crewAI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, NoSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3bd2d27d1f9c6d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software EngineerNew</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Major League Baseball</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d91f510ddbac5fdf</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee5eccf68567d950</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Major League Baseball</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb58097ec459c69e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer (C/C++) - Viasat Government</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Duluth, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, Python, R, Java, C++</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f8d027a5e350d0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Q2ebanking</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4a7be3c22ef9548</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-09.xlsx
+++ b/daily_matches/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer with AI (FTE)</t>
+          <t>Data Analyst Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Amplified Sourcing</t>
+          <t>MAP International</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Green Bay, WI, US USA</t>
+          <t>Brunswick, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, TensorFlow, BigQuery, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, S3, Glue, Athena, Redshift, Data Lake, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef6a677ec45706f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d2cecf0a7dedfc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software</t>
+          <t>Cloud Data Architect-7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Lake, LA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>27.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Prompt Engineering, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL</t>
+          <t>RAG, Azure ML, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6dcaf8ffd85fd5d</t>
+          <t>https://www.indeed.com/viewjob?jk=be1742daf9769f6b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Cloud Data Architect-7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>27.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Kafka</t>
+          <t>RAG, Azure ML, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed72dec4a4153ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a051cca67a16e478</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gen AI Engineer (Remote)-6</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Frederick, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes</t>
+          <t>RAG, S3, Glue, Redshift, Data Lake, Kinesis, Apache Airflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=742dbe1f38c1a6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=27eca6e7e11ed7f7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>GEN AI Solution Architect-6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Sentence Transformers, PyTorch, AWS SageMaker, FastAPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce4901601fc9ef85</t>
+          <t>https://www.indeed.com/viewjob?jk=72442aa34a455b8a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applications Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aries Aero Systems</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, FAISS, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, Git, Kafka, Hadoop, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d442ada28b09fb</t>
+          <t>https://www.indeed.com/viewjob?jk=0a75465cb64e7d4f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Consultant, Data Scientist | Forensic and Litigation Consulting</t>
+          <t>Gen AI Engineer-9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FTI Consulting, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, spaCy, MLflow, FastAPI, Docker, Git, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b83670379818134</t>
+          <t>https://www.indeed.com/viewjob?jk=d1dc7c76e9ecf33c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python AI</t>
+          <t>Gen AI Engineer-9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, Pinecone, Prompt Engineering, S3, EC2, Glue, FastAPI, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32db098f47b462ca</t>
+          <t>https://www.indeed.com/viewjob?jk=15fae849c8133ceb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software AI Engineer – Agentic AI-6</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Hillspire Consulting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Snowflake, BigQuery, Redshift, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b51936d889dfdd9</t>
+          <t>https://www.indeed.com/viewjob?jk=480a62ff4a821952</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GameChanger</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Data Lake, GitHub Actions, Git, Snowflake, BigQuery, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, Azure ML, Azure ML Studio, FastAPI, Kubernetes, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bdd5bca130aa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=4269a18437bfd915</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Axios</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Redford, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=208813262e2d55e5</t>
+          <t>https://www.indeed.com/viewjob?jk=33c2b0df5e54c60a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer — Builder Wanted - AI Tech Startup</t>
+          <t>Python Developer-8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FutureStack AI Inc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FastAPI, Docker, Git, Python, SQL, R</t>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0503c5c69f5d27c</t>
+          <t>https://www.indeed.com/viewjob?jk=f72794da498932c6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer – Equities Technology</t>
+          <t>Python Developer-8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>William Blair &amp; Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Synapse, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f10cecc44333b7</t>
+          <t>https://www.indeed.com/viewjob?jk=949d0f60ed86335e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Data Scientist - Applied Science</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Treeswift</t>
+          <t>Future Secure AI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, Terraform, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, spaCy, NLTK, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb8792d87cb5d68a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e4a1c03a5987</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mid-Level Engineer, Global</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, PySpark, Python, SQL, R, Scala</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6a214098e56d83</t>
+          <t>https://www.indeed.com/viewjob?jk=6c162f75ae66b790</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Systems Integration Specialist Advisor</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b38a3aeca26ed5</t>
+          <t>https://www.indeed.com/viewjob?jk=f496c222aa209b78</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Apache Airflow, CI/CD, Terraform, Git, Databricks, Python, R, Scala</t>
+          <t>Data Scientist, Copilot, Data Lake, Dataflow, CI/CD, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b09c8dba3c2b63ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b38575dad39bc4d7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>k1x</t>
+          <t>American Academy of Orthopaedic Surgeons</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, MLflow, Docker, Kubernetes, CI/CD, Git, Snowflake, Python, R, Scala</t>
+          <t>RAG, Synapse, Dataflow, CI/CD, Terraform, Git, Snowflake, PySpark, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c670dfb6481a8e15</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16d03b06a3a6a4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Deployment Engineer</t>
+          <t>AI/ML Engineer-6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>crewAI</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bd2d27d1f9c6d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ecf21497871515d1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software EngineerNew</t>
+          <t>AI/ML Engineer-6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, R, Java, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5eccf68567d950</t>
+          <t>https://www.indeed.com/viewjob?jk=edd2e347f91a2f97</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Generative AI Developer-8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Major League Baseball</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,77 +1196,987 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb58097ec459c69e</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1c95a588a4ac65</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer (C/C++) - Viasat Government</t>
+          <t>Senior Generative AI Developer-8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, Python, R, Java, C++</t>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8d027a5e350d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=898c8ef09bab8e3d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Senior Generative AI Developer-8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b24593900f3a97c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Production Support Analyst</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NAVA SOFTWARE SOLUTIONS INDIA PVT LTD</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>South Jordan, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Docker, CI/CD, Jenkins, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b2db84f225a0ac5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Deployment Engineer &amp; Coordinator</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Azure ML, Docker, Kubernetes, AKS, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46fd04300b07afb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Systems Integration</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Synapse, Git, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4c613c7dccfaf74</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer - E2E DevOps Services</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f1e10ce12fe8feb</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data Cloud Engineer(s)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Dun &amp; Bradstreet</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Terraform, Git, Snowflake, PostgreSQL, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83bec76cf3cc564d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Contract &amp; FTE both)-6</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a02c0e87c7ea0fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GenAI Engineer-6</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8ad569544b6045f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data scientist-8</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Newark, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75411038dd305023</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Athena, Redshift, Git, Redshift, NoSQL, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68eb200e81aeef9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DevOps Automation Engineer Level I</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4G Clinical</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f3b6e0ff4dc3a98</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Applied Science</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Future Secure AI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=215400ba5153b619</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Engineer II (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d7594348092c5fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Engineer II (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=086162d910624beb</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Engineer II (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da8c73f6c5e69f5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>E-Commerce Systems Engineer (Contract-to-Hire, On-Site)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Audio Icon</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Irwindale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0543d9d330cdea1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Hollstadt Consulting</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, CI/CD, Terraform, BigQuery, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35f1dfe32a19cb7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Intern, AI &amp; Automation Engineering</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Aprio</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Azure ML, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57e606a9d71ecc32</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Agentic QA Engineer / Generative AI &amp; Agentic Systems (Contract &amp; FTE)-8</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, LLaMA, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2d4a5e465bfe484</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Q2ebanking</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>10</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, Snowflake, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a7be3c22ef9548</t>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=565b9cd99d1356b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Systems Integration Senior Specialist</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7563b545ab1c8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI Search Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, AKS, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31a45e1b3d2ae45a</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Versant</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Git, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a942d52d80263a6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Test Automation Engineer(Web)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Research Innovations Inc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Alexandria, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c06478204d72ad1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Java AI Engineer-6</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90cea4a064452161</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer-9</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3887d4ee68910fb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Data Scientist-8</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Data Scientist, PySpark, Kafka, Hadoop, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1969a5af1b3ab507</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-09.xlsx
+++ b/daily_matches/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Analyst Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAP International</t>
+          <t>PACCAR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brunswick, GA, US USA</t>
+          <t>Chillicothe, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, S3, Glue, Athena, Redshift, Data Lake, Docker</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d2cecf0a7dedfc</t>
+          <t>https://www.indeed.com/viewjob?jk=2a7aa9de7ae098db</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Data Architect-7</t>
+          <t>AI Architect - IT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Boston Energy Trading and Marketing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>West Lake, LA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1742daf9769f6b</t>
+          <t>https://www.indeed.com/viewjob?jk=351a87f9d4d66fed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Data Architect-7</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a051cca67a16e478</t>
+          <t>https://www.indeed.com/viewjob?jk=03998723d307f031</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>CURIE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, Kinesis, Apache Airflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27eca6e7e11ed7f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1812dda95c32d103</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GEN AI Solution Architect-6</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CURIE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Sentence Transformers, PyTorch, AWS SageMaker, FastAPI</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72442aa34a455b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=07a8fc25764c9d91</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CURIE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, Git, Kafka, Hadoop, NoSQL, Tableau</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a75465cb64e7d4f</t>
+          <t>https://www.indeed.com/viewjob?jk=eddf92ebc2a2eb11</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-9</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CURIE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1dc7c76e9ecf33c</t>
+          <t>https://www.indeed.com/viewjob?jk=0719d5fe88584102</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-9</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Walkme</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fae849c8133ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=675aa75207b1417e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python AI Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hillspire Consulting</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Snowflake, BigQuery, Redshift, Kafka, Hadoop</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Seaborn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=480a62ff4a821952</t>
+          <t>https://www.indeed.com/viewjob?jk=87d9fad02cb9d0db</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, Azure ML, Azure ML Studio, FastAPI, Kubernetes, Terraform</t>
+          <t>Data Scientist, MLflow, Docker, CI/CD, Git, Databricks, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4269a18437bfd915</t>
+          <t>https://www.indeed.com/viewjob?jk=8973c147c241b3e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Solution Sales Specialist - AIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Redford, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Python, SQL</t>
+          <t>Data Scientist, Gemini, Copilot, TensorFlow, AWS SageMaker, BigQuery, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c2b0df5e54c60a</t>
+          <t>https://www.indeed.com/viewjob?jk=2faa67b1e624e2b2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python Developer-8</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>Data Scientist, Data Lake, Git, Databricks, Kafka, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72794da498932c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f9725451a4b09d99</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Developer-8</t>
+          <t>Engineer Full stack development</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Okmulgee, OK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>Data Scientist, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=949d0f60ed86335e</t>
+          <t>https://www.indeed.com/viewjob?jk=c34e52ba65b040b9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist - Applied Science</t>
+          <t>Applied Data Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Future Secure AI</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, spaCy, NLTK, Python, SQL, R</t>
+          <t>LangChain, RAG, CI/CD, Git, Snowflake, PySpark, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e4a1c03a5987</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbb38f96c262fe4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Platform Engineer (AWS)</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OpenVPN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Copilot, Azure ML, BigQuery, Kubernetes, Terraform, Git, BigQuery, Kafka, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c162f75ae66b790</t>
+          <t>https://www.indeed.com/viewjob?jk=8d792b6a291b9b49</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Systems Integration Specialist Advisor</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OpenVPN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python</t>
+          <t>RAG, Copilot, Azure ML, BigQuery, Kubernetes, Terraform, Git, BigQuery, Kafka, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f496c222aa209b78</t>
+          <t>https://www.indeed.com/viewjob?jk=c01257a1a3bb5f26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>Future Secure AI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, Data Lake, Dataflow, CI/CD, Snowflake, Power BI, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b38575dad39bc4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=67a4198a5db8043d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Simulation Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Academy of Orthopaedic Surgeons</t>
+          <t>UnitX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Dataflow, CI/CD, Terraform, Git, Snowflake, PySpark, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd16d03b06a3a6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a70d88e035abaf4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI/ML Engineer-6</t>
+          <t>Software Developer II - Customer Care &amp; Billing Utility Software (Front End)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python</t>
+          <t>Generative AI, RAG, Kubernetes, Git, Kafka, Cassandra, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecf21497871515d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c620f2a995d70772</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI/ML Engineer-6</t>
+          <t>Sr. Angular Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python</t>
+          <t>RAG, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edd2e347f91a2f97</t>
+          <t>https://www.indeed.com/viewjob?jk=5b1a5d8ed39b8478</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer-8</t>
+          <t>Sr. Solutions Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Future Secure AI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1c95a588a4ac65</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad753f3ce6ad143</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer-8</t>
+          <t>Senior Full-Stack Engineer, AI Financial Actions &amp; Recommendations</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898c8ef09bab8e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=f683951395d00b4f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer-8</t>
+          <t>Research Engineer, Applied AI Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>NACTUS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b24593900f3a97c7</t>
+          <t>https://www.indeed.com/viewjob?jk=240dcbc3eefcff5e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Production Support Analyst</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NAVA SOFTWARE SOLUTIONS INDIA PVT LTD</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Jenkins, Git, Snowflake, Kafka, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, XGBoost, Keras, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2db84f225a0ac5</t>
+          <t>https://www.indeed.com/viewjob?jk=4033d0202ba802ca</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deployment Engineer &amp; Coordinator</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, Docker, Kubernetes, AKS, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>LangChain, RAG, LLaMA, TensorFlow, Docker, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46fd04300b07afb0</t>
+          <t>https://www.indeed.com/viewjob?jk=90a1c10ed9f35b39</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Systems Integration</t>
+          <t>Integration Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Synapse, Git, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, TensorFlow, Docker, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4c613c7dccfaf74</t>
+          <t>https://www.indeed.com/viewjob?jk=430029b8425ee59c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - E2E DevOps Services</t>
+          <t>Senior Machine Learning Engineer - Computer Vision</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Leverege</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Scala, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,777 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e10ce12fe8feb</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Data Cloud Engineer(s)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Dun &amp; Bradstreet</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Terraform, Git, Snowflake, PostgreSQL, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83bec76cf3cc564d</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer (Contract &amp; FTE both)-6</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Databricks, Python, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a02c0e87c7ea0fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>GenAI Engineer-6</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ad569544b6045f</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data scientist-8</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Newark, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75411038dd305023</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Scientist, Athena, Redshift, Git, Redshift, NoSQL, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68eb200e81aeef9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>DevOps Automation Engineer Level I</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4G Clinical</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3b6e0ff4dc3a98</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Applied Science</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Future Secure AI</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=215400ba5153b619</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Engineer II (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d7594348092c5fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Engineer II (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=086162d910624beb</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Engineer II (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da8c73f6c5e69f5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>E-Commerce Systems Engineer (Contract-to-Hire, On-Site)</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Audio Icon</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Irwindale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0543d9d330cdea1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Hollstadt Consulting</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>MN, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, CI/CD, Terraform, BigQuery, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35f1dfe32a19cb7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Intern, AI &amp; Automation Engineering</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Aprio</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Azure ML, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57e606a9d71ecc32</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Agentic QA Engineer / Generative AI &amp; Agentic Systems (Contract &amp; FTE)-8</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, LLaMA, CI/CD, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2d4a5e465bfe484</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=565b9cd99d1356b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Systems Integration Senior Specialist</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7563b545ab1c8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>AI Search Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>FastAPI, Docker, Kubernetes, AKS, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31a45e1b3d2ae45a</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Versant</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, Git, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a942d52d80263a6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Test Automation Engineer(Web)</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Research Innovations Inc</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Alexandria, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c06478204d72ad1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Java AI Engineer-6</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90cea4a064452161</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Agentic AI Engineer-9</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3887d4ee68910fb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Data Scientist-8</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Data Scientist, PySpark, Kafka, Hadoop, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1969a5af1b3ab507</t>
+          <t>https://www.indeed.com/viewjob?jk=612f99797ebea512</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-09.xlsx
+++ b/daily_matches/job_matches_2026-04-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Prompt Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PACCAR</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chillicothe, OH, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Gemini, Copilot, FAISS, Pinecone, Prompt Engineering, S3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7aa9de7ae098db</t>
+          <t>https://www.indeed.com/viewjob?jk=41cffd5798f04845</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Architect - IT</t>
+          <t>Machine Learning Engineer, Specialist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Boston Energy Trading and Marketing</t>
+          <t>Vanguard</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, BigQuery</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, S3, EC2, Glue, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351a87f9d4d66fed</t>
+          <t>https://www.indeed.com/viewjob?jk=74e743e45605a878</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, AKS, CI/CD, Git, Snowflake, MongoDB, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03998723d307f031</t>
+          <t>https://www.indeed.com/viewjob?jk=6abb2385899cf65f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer, Revenue Intelligence</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CURIE</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
+          <t>RAG, Copilot, Synapse, Docker, CI/CD, GitHub Actions, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1812dda95c32d103</t>
+          <t>https://www.indeed.com/viewjob?jk=5f11c5f49ca38408</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Agent Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CURIE</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, S3, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a8fc25764c9d91</t>
+          <t>https://www.indeed.com/viewjob?jk=1c6074e1e39d72ee</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CURIE</t>
+          <t>Border States Electric</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eddf92ebc2a2eb11</t>
+          <t>https://www.indeed.com/viewjob?jk=76333d6eedada6d6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Business Systems Automation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CURIE</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Git, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0719d5fe88584102</t>
+          <t>https://www.indeed.com/viewjob?jk=1ac4ee19d0b4ce79</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675aa75207b1417e</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb2064fa7d1ef15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python AI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Seaborn</t>
+          <t>Kubernetes, CI/CD, Git, Snowflake, Kafka, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87d9fad02cb9d0db</t>
+          <t>https://www.indeed.com/viewjob?jk=89ffd3b61632831c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Intern, Software Engineer-AI Agents</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, MLflow, Docker, CI/CD, Git, Databricks, NoSQL, Python, SQL, R</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973c147c241b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=57736f7bcb05c17a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Solution Sales Specialist - AIA</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Gemini, Copilot, TensorFlow, AWS SageMaker, BigQuery, Git, Snowflake, Databricks, BigQuery</t>
+          <t>Databricks, PySpark, MongoDB, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2faa67b1e624e2b2</t>
+          <t>https://www.indeed.com/viewjob?jk=8c18410d10e98da8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Track Associate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Data Lake, Git, Databricks, Kafka, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9725451a4b09d99</t>
+          <t>https://www.indeed.com/viewjob?jk=402c953eefad81a6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer Full stack development</t>
+          <t>Sr Technical Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>PARAMOUNT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Okmulgee, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c34e52ba65b040b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b10425fb7854d238</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Applied Data Analyst</t>
+          <t>Sr Technical Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>PARAMOUNT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, CI/CD, Git, Snowflake, PySpark, Tableau, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbb38f96c262fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=79f9540f46e40605</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OpenVPN</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Azure ML, BigQuery, Kubernetes, Terraform, Git, BigQuery, Kafka, R</t>
+          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d792b6a291b9b49</t>
+          <t>https://www.indeed.com/viewjob?jk=84ccdb8bd4f05a4d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Data Architect - Paid Relocation to Cincinnati</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OpenVPN</t>
+          <t>Total Quality Logistics (TQL)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Azure ML, BigQuery, Kubernetes, Terraform, Git, BigQuery, Kafka, R</t>
+          <t>RAG, Synapse, Databricks, Kafka, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01257a1a3bb5f26</t>
+          <t>https://www.indeed.com/viewjob?jk=36d097a5c9b38547</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Full Stack Developer (AI Focus)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Future Secure AI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,357 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a4198a5db8043d</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Simulation Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>UnitX</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Milpitas, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a70d88e035abaf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Developer II - Customer Care &amp; Billing Utility Software (Front End)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, Git, Kafka, Cassandra, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c620f2a995d70772</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sr. Angular Developer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b1a5d8ed39b8478</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Future Secure AI</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad753f3ce6ad143</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Full-Stack Engineer, AI Financial Actions &amp; Recommendations</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, PostgreSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f683951395d00b4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Research Engineer, Applied AI Engineering</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NACTUS</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=240dcbc3eefcff5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Instacart</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, XGBoost, Keras, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4033d0202ba802ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Ericsson</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, TensorFlow, Docker, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90a1c10ed9f35b39</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Ericsson</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, TensorFlow, Docker, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=430029b8425ee59c</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer - Computer Vision</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Leverege</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Scala, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612f99797ebea512</t>
+          <t>https://www.indeed.com/viewjob?jk=78cc161803030f68</t>
         </is>
       </c>
     </row>
